--- a/notification_VIDE.xlsx
+++ b/notification_VIDE.xlsx
@@ -459,18 +459,24 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
+      <c r="A2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>Bob</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
           <t>VIDE</t>
@@ -486,27 +492,41 @@
           <t>2000</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
+      <c r="A3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>Charlie</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>VIDE</t>
